--- a/data/4-reports/5_DOID_Mapping.xlsx
+++ b/data/4-reports/5_DOID_Mapping.xlsx
@@ -740,17 +740,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>autoimmune interstitial lung, joint, and kidney disease</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
